--- a/xls/square_un_16_tri3_14.xlsx
+++ b/xls/square_un_16_tri3_14.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>256</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>340</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>209</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>1104</v>
+      </c>
+      <c r="I12">
+        <v>-0.00022188852579196067</v>
+      </c>
+      <c r="J12">
+        <v>-1.5912266338219745</v>
+      </c>
+      <c r="K12">
+        <v>0.37726726548059875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>256</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>340</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>238</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>1266</v>
+      </c>
+      <c r="I13">
+        <v>-0.00019993540712612352</v>
+      </c>
+      <c r="J13">
+        <v>-1.0522063567639788</v>
+      </c>
+      <c r="K13">
+        <v>1.2186098502543115</v>
+      </c>
+    </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>11</v>
       </c>
       <c r="B14">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F14">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
       </c>
       <c r="H14">
-        <v>1176</v>
+        <v>1362</v>
       </c>
       <c r="I14">
-        <v>-1.8209395319789132</v>
+        <v>-0.00018527676775155505</v>
       </c>
       <c r="J14">
-        <v>-1.9549356118379289</v>
+        <v>-0.871595693603983</v>
       </c>
       <c r="K14">
-        <v>-0.7990056416019369</v>
+        <v>1.3358005405176334</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F15">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15">
-        <v>1350</v>
+        <v>1596</v>
       </c>
       <c r="I15">
-        <v>-2.235650474757881</v>
+        <v>-0.00016188043330657838</v>
       </c>
       <c r="J15">
-        <v>-2.1142264856193917</v>
+        <v>-0.6572168127916598</v>
       </c>
       <c r="K15">
-        <v>-0.8523051584967096</v>
+        <v>2.0630898194345835</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F16">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1536</v>
+        <v>1842</v>
       </c>
       <c r="I16">
-        <v>-2.591654526596785</v>
+        <v>-9.427521014430726e-5</v>
       </c>
       <c r="J16">
-        <v>-2.1591949954498224</v>
+        <v>-0.3170013141010657</v>
       </c>
       <c r="K16">
-        <v>-0.6564705244438996</v>
+        <v>2.9454787460720846</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B17">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F17">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17">
-        <v>1734</v>
+        <v>2070</v>
       </c>
       <c r="I17">
-        <v>-2.4751653357932466</v>
+        <v>-2.0829527040588577e-5</v>
       </c>
       <c r="J17">
-        <v>-1.9509891783791975</v>
+        <v>-0.056267606747010035</v>
       </c>
       <c r="K17">
-        <v>-0.17826366601467977</v>
+        <v>3.112858099491669</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B18">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F18">
-        <v>361</v>
+        <v>435</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18">
-        <v>1944</v>
+        <v>2388</v>
       </c>
       <c r="I18">
-        <v>-1.8982525656621099</v>
+        <v>-4.6243636626433305e-8</v>
       </c>
       <c r="J18">
-        <v>-1.539191173330576</v>
+        <v>-0.0001004401491271084</v>
       </c>
       <c r="K18">
-        <v>0.7852187811821948</v>
+        <v>2.4131428388916576</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B19">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19">
-        <v>2166</v>
+        <v>2676</v>
       </c>
       <c r="I19">
-        <v>-0.8723643404133086</v>
+        <v>-3.0288061980960263e-9</v>
       </c>
       <c r="J19">
-        <v>-0.7334074881493385</v>
+        <v>-5.4924198586650055e-6</v>
       </c>
       <c r="K19">
-        <v>1.7636488952001677</v>
+        <v>1.7929859382096287</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B20">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F20">
-        <v>441</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20">
-        <v>2400</v>
+        <v>3138</v>
       </c>
       <c r="I20">
-        <v>-0.0428778812547181</v>
+        <v>-1.060961614295946e-9</v>
       </c>
       <c r="J20">
-        <v>-0.05691253441818859</v>
+        <v>-1.7350578973987236e-6</v>
       </c>
       <c r="K20">
-        <v>2.8652801618640056</v>
+        <v>1.5460072061209582</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B21">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-1.7046592518613962e-5</v>
+        <v>-7.463079258661889e-10</v>
       </c>
       <c r="J21">
-        <v>-0.0002170938630220543</v>
+        <v>-1.21515325604603e-6</v>
       </c>
       <c r="K21">
-        <v>2.7670450110657665</v>
+        <v>1.4683333270774128</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-2.552537695532524e-5</v>
+        <v>-4.725612017036724e-10</v>
       </c>
       <c r="J22">
-        <v>-4.293995994790839e-5</v>
+        <v>-8.332799374392817e-7</v>
       </c>
       <c r="K22">
-        <v>2.3627087054894806</v>
+        <v>1.3979324418621304</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-1.543586149615669e-5</v>
+        <v>-2.771502694436345e-10</v>
       </c>
       <c r="J23">
-        <v>-2.081513558352663e-5</v>
+        <v>-5.408230908514371e-7</v>
       </c>
       <c r="K23">
-        <v>2.1815742825646107</v>
+        <v>1.314914146123434</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -811,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-1.0780104795134298e-5</v>
+        <v>-2.8392023399419826e-10</v>
       </c>
       <c r="J24">
-        <v>-1.4355760818072221e-5</v>
+        <v>-5.339369636251535e-7</v>
       </c>
       <c r="K24">
-        <v>2.0922578857238885</v>
+        <v>1.3080640875908882</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -846,7 +916,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-7.754387230963765e-6</v>
+        <v>-2.349752630199398e-10</v>
       </c>
       <c r="J25">
-        <v>-1.0450728120655955e-5</v>
+        <v>-4.4657922979247013e-7</v>
       </c>
       <c r="K25">
-        <v>2.0297726578466277</v>
+        <v>1.2734584544565617</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -881,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -893,22 +963,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-8.806824280928771e-6</v>
+        <v>-2.2603594740024625e-10</v>
       </c>
       <c r="J26">
-        <v>-1.129501312990995e-5</v>
+        <v>-4.2487194871653025e-7</v>
       </c>
       <c r="K26">
-        <v>2.0361454885767465</v>
+        <v>1.2613432047236075</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -916,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -928,22 +998,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-3.882955798296005e-6</v>
+        <v>-2.0754602898007037e-10</v>
       </c>
       <c r="J27">
-        <v>-5.2424876754834725e-6</v>
+        <v>-4.0380317951243973e-7</v>
       </c>
       <c r="K27">
-        <v>1.872747842331496</v>
+        <v>1.252578392747417</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -951,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -963,22 +1033,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-4.070670650596052e-6</v>
+        <v>-2.0578449199607924e-10</v>
       </c>
       <c r="J28">
-        <v>-5.0965038080164965e-6</v>
+        <v>-3.910940216075901e-7</v>
       </c>
       <c r="K28">
-        <v>1.8551916561118826</v>
+        <v>1.2444181686247966</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -986,7 +1056,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -998,22 +1068,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-2.766305754573751e-6</v>
+        <v>-1.9617583668214898e-10</v>
       </c>
       <c r="J29">
-        <v>-3.6550036837921876e-6</v>
+        <v>-3.7062206375346877e-7</v>
       </c>
       <c r="K29">
-        <v>1.797540913639804</v>
+        <v>1.2325460929140402</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1021,7 +1091,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -1033,22 +1103,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-2.9487073393979016e-6</v>
+        <v>-1.7804141758393486e-10</v>
       </c>
       <c r="J30">
-        <v>-3.6363481701566937e-6</v>
+        <v>-3.3853282648616937e-7</v>
       </c>
       <c r="K30">
-        <v>1.7780863308106554</v>
+        <v>1.2135246673249345</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1056,7 +1126,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -1068,22 +1138,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-1.8626968453846168e-6</v>
+        <v>-1.6705777595190234e-10</v>
       </c>
       <c r="J31">
-        <v>-2.2785655309985517e-6</v>
+        <v>-3.1943219669010053e-7</v>
       </c>
       <c r="K31">
-        <v>1.6751492239456494</v>
+        <v>1.2020271520116306</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1091,7 +1161,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1103,22 +1173,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-2.18831248384343e-6</v>
+        <v>-1.6409926749976224e-10</v>
       </c>
       <c r="J32">
-        <v>-2.340825136377812e-6</v>
+        <v>-3.142959223658438e-7</v>
       </c>
       <c r="K32">
-        <v>1.6512069393585689</v>
+        <v>1.1988140628101562</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_14.xlsx
+++ b/xls/square_un_16_tri3_14.xlsx
@@ -461,34 +461,34 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
       </c>
       <c r="F16">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1842</v>
+        <v>1596</v>
       </c>
       <c r="I16">
-        <v>-1.8140567624405977</v>
+        <v>-1.7266035504655097</v>
       </c>
       <c r="J16">
-        <v>-1.9344540368965966</v>
+        <v>-2.0094163176931596</v>
       </c>
       <c r="K16">
-        <v>-1.5262618161138641</v>
+        <v>-1.563756856730796</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_14.xlsx
+++ b/xls/square_un_16_tri3_14.xlsx
@@ -482,13 +482,13 @@
         <v>1596</v>
       </c>
       <c r="I16">
-        <v>-1.7266035504655097</v>
+        <v>-2.0865303143151412</v>
       </c>
       <c r="J16">
-        <v>-2.0094163176931596</v>
+        <v>-1.7746815496210704</v>
       </c>
       <c r="K16">
-        <v>-1.563756856730796</v>
+        <v>-0.422972193242754</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_14.xlsx
+++ b/xls/square_un_16_tri3_14.xlsx
@@ -482,13 +482,13 @@
         <v>1596</v>
       </c>
       <c r="I16">
-        <v>-1.7266035504655097</v>
+        <v>-2.020280575960859</v>
       </c>
       <c r="J16">
-        <v>-2.0094163176931596</v>
+        <v>-1.7357518278207746</v>
       </c>
       <c r="K16">
-        <v>-1.563756856730796</v>
+        <v>-0.4077441347614383</v>
       </c>
     </row>
   </sheetData>
